--- a/GSK.xlsx
+++ b/GSK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF139AD6-4D3B-4DE2-8102-7818EC0AD6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B0E6AA-1581-451D-B80C-B690AA709C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27285" yWindow="555" windowWidth="26115" windowHeight="20010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14410" yWindow="4280" windowWidth="19050" windowHeight="16100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="59" r:id="rId1"/>
@@ -3885,7 +3885,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="1505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="1506">
   <si>
     <t>Indication</t>
   </si>
@@ -8506,6 +8506,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -9334,32 +9337,41 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -9368,15 +9380,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14918,11 +14921,11 @@
       </c>
     </row>
     <row r="61" spans="3:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="197"/>
-      <c r="D61" s="195" t="s">
+      <c r="C61" s="193"/>
+      <c r="D61" s="204" t="s">
         <v>457</v>
       </c>
-      <c r="E61" s="195"/>
+      <c r="E61" s="204"/>
       <c r="F61"/>
       <c r="G61"/>
       <c r="H61"/>
@@ -14931,9 +14934,9 @@
       <c r="K61"/>
     </row>
     <row r="62" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C62" s="197"/>
-      <c r="D62" s="195"/>
-      <c r="E62" s="195"/>
+      <c r="C62" s="193"/>
+      <c r="D62" s="204"/>
+      <c r="E62" s="204"/>
       <c r="F62"/>
       <c r="G62"/>
       <c r="H62"/>
@@ -14942,246 +14945,246 @@
       <c r="K62"/>
     </row>
     <row r="63" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C63" s="197"/>
-      <c r="D63" s="198"/>
-      <c r="E63" s="198"/>
-      <c r="F63" s="198"/>
-      <c r="G63" s="198"/>
-      <c r="H63" s="198"/>
-      <c r="I63" s="198"/>
-      <c r="J63" s="198"/>
-      <c r="K63" s="198"/>
+      <c r="C63" s="193"/>
+      <c r="D63" s="194"/>
+      <c r="E63" s="194"/>
+      <c r="F63" s="194"/>
+      <c r="G63" s="194"/>
+      <c r="H63" s="194"/>
+      <c r="I63" s="194"/>
+      <c r="J63" s="194"/>
+      <c r="K63" s="194"/>
     </row>
     <row r="64" spans="3:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="197"/>
-      <c r="D64" s="194" t="s">
+      <c r="C64" s="193"/>
+      <c r="D64" s="195" t="s">
         <v>458</v>
       </c>
-      <c r="E64" s="196" t="s">
+      <c r="E64" s="203" t="s">
         <v>459</v>
       </c>
-      <c r="F64" s="201"/>
-      <c r="G64" s="201"/>
-      <c r="H64" s="201"/>
-      <c r="I64" s="201"/>
-      <c r="J64" s="201"/>
-      <c r="K64" s="201"/>
+      <c r="F64" s="198"/>
+      <c r="G64" s="198"/>
+      <c r="H64" s="198"/>
+      <c r="I64" s="198"/>
+      <c r="J64" s="198"/>
+      <c r="K64" s="198"/>
     </row>
     <row r="65" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C65" s="197"/>
-      <c r="D65" s="194"/>
-      <c r="E65" s="196"/>
-      <c r="F65" s="201"/>
-      <c r="G65" s="201"/>
-      <c r="H65" s="201"/>
-      <c r="I65" s="201"/>
-      <c r="J65" s="201"/>
-      <c r="K65" s="201"/>
+      <c r="C65" s="193"/>
+      <c r="D65" s="195"/>
+      <c r="E65" s="203"/>
+      <c r="F65" s="198"/>
+      <c r="G65" s="198"/>
+      <c r="H65" s="198"/>
+      <c r="I65" s="198"/>
+      <c r="J65" s="198"/>
+      <c r="K65" s="198"/>
     </row>
     <row r="66" spans="3:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="197"/>
-      <c r="D66" s="194" t="s">
+      <c r="C66" s="193"/>
+      <c r="D66" s="195" t="s">
         <v>460</v>
       </c>
-      <c r="E66" s="193" t="s">
+      <c r="E66" s="197" t="s">
         <v>461</v>
       </c>
-      <c r="F66" s="201"/>
-      <c r="G66" s="201"/>
-      <c r="H66" s="201"/>
-      <c r="I66" s="201"/>
-      <c r="J66" s="201"/>
-      <c r="K66" s="201"/>
+      <c r="F66" s="198"/>
+      <c r="G66" s="198"/>
+      <c r="H66" s="198"/>
+      <c r="I66" s="198"/>
+      <c r="J66" s="198"/>
+      <c r="K66" s="198"/>
     </row>
     <row r="67" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C67" s="197"/>
-      <c r="D67" s="194"/>
-      <c r="E67" s="193"/>
-      <c r="F67" s="201"/>
-      <c r="G67" s="201"/>
-      <c r="H67" s="201"/>
-      <c r="I67" s="201"/>
-      <c r="J67" s="201"/>
-      <c r="K67" s="201"/>
+      <c r="C67" s="193"/>
+      <c r="D67" s="195"/>
+      <c r="E67" s="197"/>
+      <c r="F67" s="198"/>
+      <c r="G67" s="198"/>
+      <c r="H67" s="198"/>
+      <c r="I67" s="198"/>
+      <c r="J67" s="198"/>
+      <c r="K67" s="198"/>
     </row>
     <row r="68" spans="3:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="197"/>
-      <c r="D68" s="194" t="s">
+      <c r="C68" s="193"/>
+      <c r="D68" s="195" t="s">
         <v>462</v>
       </c>
-      <c r="E68" s="196" t="s">
+      <c r="E68" s="203" t="s">
         <v>463</v>
       </c>
-      <c r="F68" s="201"/>
-      <c r="G68" s="201"/>
-      <c r="H68" s="201"/>
-      <c r="I68" s="201"/>
-      <c r="J68" s="201"/>
-      <c r="K68" s="201"/>
+      <c r="F68" s="198"/>
+      <c r="G68" s="198"/>
+      <c r="H68" s="198"/>
+      <c r="I68" s="198"/>
+      <c r="J68" s="198"/>
+      <c r="K68" s="198"/>
     </row>
     <row r="69" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C69" s="197"/>
-      <c r="D69" s="194"/>
-      <c r="E69" s="196"/>
-      <c r="F69" s="201"/>
-      <c r="G69" s="201"/>
-      <c r="H69" s="201"/>
-      <c r="I69" s="201"/>
-      <c r="J69" s="201"/>
-      <c r="K69" s="201"/>
+      <c r="C69" s="193"/>
+      <c r="D69" s="195"/>
+      <c r="E69" s="203"/>
+      <c r="F69" s="198"/>
+      <c r="G69" s="198"/>
+      <c r="H69" s="198"/>
+      <c r="I69" s="198"/>
+      <c r="J69" s="198"/>
+      <c r="K69" s="198"/>
     </row>
     <row r="70" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C70" s="197"/>
-      <c r="D70" s="198"/>
-      <c r="E70" s="198"/>
-      <c r="F70" s="198"/>
-      <c r="G70" s="198"/>
-      <c r="H70" s="198"/>
-      <c r="I70" s="198"/>
-      <c r="J70" s="198"/>
-      <c r="K70" s="198"/>
+      <c r="C70" s="193"/>
+      <c r="D70" s="194"/>
+      <c r="E70" s="194"/>
+      <c r="F70" s="194"/>
+      <c r="G70" s="194"/>
+      <c r="H70" s="194"/>
+      <c r="I70" s="194"/>
+      <c r="J70" s="194"/>
+      <c r="K70" s="194"/>
     </row>
     <row r="71" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C71" s="197"/>
-      <c r="D71" s="197"/>
-      <c r="E71" s="197"/>
-      <c r="F71" s="197"/>
-      <c r="G71" s="197"/>
-      <c r="H71" s="197"/>
-      <c r="I71" s="197"/>
-      <c r="J71" s="197"/>
-      <c r="K71" s="197"/>
+      <c r="C71" s="193"/>
+      <c r="D71" s="193"/>
+      <c r="E71" s="193"/>
+      <c r="F71" s="193"/>
+      <c r="G71" s="193"/>
+      <c r="H71" s="193"/>
+      <c r="I71" s="193"/>
+      <c r="J71" s="193"/>
+      <c r="K71" s="193"/>
     </row>
     <row r="72" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C72" s="197"/>
-      <c r="D72" s="197"/>
-      <c r="E72" s="197"/>
-      <c r="F72" s="197"/>
-      <c r="G72" s="197"/>
-      <c r="H72" s="197"/>
-      <c r="I72" s="197"/>
-      <c r="J72" s="197"/>
-      <c r="K72" s="197"/>
+      <c r="C72" s="193"/>
+      <c r="D72" s="193"/>
+      <c r="E72" s="193"/>
+      <c r="F72" s="193"/>
+      <c r="G72" s="193"/>
+      <c r="H72" s="193"/>
+      <c r="I72" s="193"/>
+      <c r="J72" s="193"/>
+      <c r="K72" s="193"/>
     </row>
     <row r="73" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C73" s="197"/>
-      <c r="D73" s="197"/>
-      <c r="E73" s="197"/>
-      <c r="F73" s="197"/>
-      <c r="G73" s="197"/>
-      <c r="H73" s="197"/>
-      <c r="I73" s="197"/>
-      <c r="J73" s="197"/>
-      <c r="K73" s="197"/>
+      <c r="C73" s="193"/>
+      <c r="D73" s="193"/>
+      <c r="E73" s="193"/>
+      <c r="F73" s="193"/>
+      <c r="G73" s="193"/>
+      <c r="H73" s="193"/>
+      <c r="I73" s="193"/>
+      <c r="J73" s="193"/>
+      <c r="K73" s="193"/>
     </row>
     <row r="74" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C74" s="197"/>
-      <c r="D74" s="194" t="s">
+      <c r="C74" s="193"/>
+      <c r="D74" s="195" t="s">
         <v>464</v>
       </c>
-      <c r="E74" s="194"/>
-      <c r="F74" s="193">
+      <c r="E74" s="195"/>
+      <c r="F74" s="197">
         <v>1015</v>
       </c>
-      <c r="G74" s="193"/>
-      <c r="H74" s="193"/>
-      <c r="I74" s="193"/>
-      <c r="J74" s="193"/>
-      <c r="K74" s="193"/>
+      <c r="G74" s="197"/>
+      <c r="H74" s="197"/>
+      <c r="I74" s="197"/>
+      <c r="J74" s="197"/>
+      <c r="K74" s="197"/>
     </row>
     <row r="75" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C75" s="197"/>
-      <c r="D75" s="194"/>
-      <c r="E75" s="194"/>
-      <c r="F75" s="193"/>
-      <c r="G75" s="193"/>
-      <c r="H75" s="193"/>
-      <c r="I75" s="193"/>
-      <c r="J75" s="193"/>
-      <c r="K75" s="193"/>
+      <c r="C75" s="193"/>
+      <c r="D75" s="195"/>
+      <c r="E75" s="195"/>
+      <c r="F75" s="197"/>
+      <c r="G75" s="197"/>
+      <c r="H75" s="197"/>
+      <c r="I75" s="197"/>
+      <c r="J75" s="197"/>
+      <c r="K75" s="197"/>
     </row>
     <row r="76" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C76" s="197"/>
-      <c r="D76" s="194" t="s">
+      <c r="C76" s="193"/>
+      <c r="D76" s="195" t="s">
         <v>465</v>
       </c>
-      <c r="E76" s="194"/>
-      <c r="F76" s="199" t="s">
+      <c r="E76" s="195"/>
+      <c r="F76" s="196" t="s">
         <v>466</v>
       </c>
-      <c r="G76" s="199"/>
-      <c r="H76" s="199"/>
-      <c r="I76" s="199"/>
-      <c r="J76" s="199"/>
-      <c r="K76" s="199"/>
+      <c r="G76" s="196"/>
+      <c r="H76" s="196"/>
+      <c r="I76" s="196"/>
+      <c r="J76" s="196"/>
+      <c r="K76" s="196"/>
     </row>
     <row r="77" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C77" s="197"/>
-      <c r="D77" s="194"/>
-      <c r="E77" s="194"/>
-      <c r="F77" s="199"/>
-      <c r="G77" s="199"/>
-      <c r="H77" s="199"/>
-      <c r="I77" s="199"/>
-      <c r="J77" s="199"/>
-      <c r="K77" s="199"/>
+      <c r="C77" s="193"/>
+      <c r="D77" s="195"/>
+      <c r="E77" s="195"/>
+      <c r="F77" s="196"/>
+      <c r="G77" s="196"/>
+      <c r="H77" s="196"/>
+      <c r="I77" s="196"/>
+      <c r="J77" s="196"/>
+      <c r="K77" s="196"/>
     </row>
     <row r="78" spans="3:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C78" s="197"/>
-      <c r="D78" s="194" t="s">
+      <c r="C78" s="193"/>
+      <c r="D78" s="195" t="s">
         <v>467</v>
       </c>
-      <c r="E78" s="194"/>
-      <c r="F78" s="193" t="s">
+      <c r="E78" s="195"/>
+      <c r="F78" s="197" t="s">
         <v>468</v>
       </c>
-      <c r="G78" s="193"/>
-      <c r="H78" s="193"/>
-      <c r="I78" s="193"/>
-      <c r="J78" s="193"/>
-      <c r="K78" s="193"/>
+      <c r="G78" s="197"/>
+      <c r="H78" s="197"/>
+      <c r="I78" s="197"/>
+      <c r="J78" s="197"/>
+      <c r="K78" s="197"/>
     </row>
     <row r="79" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C79" s="197"/>
-      <c r="D79" s="194"/>
-      <c r="E79" s="194"/>
-      <c r="F79" s="193"/>
-      <c r="G79" s="193"/>
-      <c r="H79" s="193"/>
-      <c r="I79" s="193"/>
-      <c r="J79" s="193"/>
-      <c r="K79" s="193"/>
+      <c r="C79" s="193"/>
+      <c r="D79" s="195"/>
+      <c r="E79" s="195"/>
+      <c r="F79" s="197"/>
+      <c r="G79" s="197"/>
+      <c r="H79" s="197"/>
+      <c r="I79" s="197"/>
+      <c r="J79" s="197"/>
+      <c r="K79" s="197"/>
     </row>
     <row r="80" spans="3:11" ht="202.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C80" s="197"/>
-      <c r="D80" s="194" t="s">
+      <c r="C80" s="193"/>
+      <c r="D80" s="195" t="s">
         <v>469</v>
       </c>
-      <c r="E80" s="194"/>
-      <c r="F80" s="193" t="s">
+      <c r="E80" s="195"/>
+      <c r="F80" s="197" t="s">
         <v>470</v>
       </c>
-      <c r="G80" s="193"/>
-      <c r="H80" s="193"/>
-      <c r="I80" s="193"/>
-      <c r="J80" s="193"/>
-      <c r="K80" s="193"/>
+      <c r="G80" s="197"/>
+      <c r="H80" s="197"/>
+      <c r="I80" s="197"/>
+      <c r="J80" s="197"/>
+      <c r="K80" s="197"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C81" s="197"/>
-      <c r="D81" s="194"/>
-      <c r="E81" s="194"/>
-      <c r="F81" s="200"/>
-      <c r="G81" s="200"/>
-      <c r="H81" s="200"/>
-      <c r="I81" s="200"/>
-      <c r="J81" s="200"/>
-      <c r="K81" s="200"/>
+      <c r="C81" s="193"/>
+      <c r="D81" s="195"/>
+      <c r="E81" s="195"/>
+      <c r="F81" s="202"/>
+      <c r="G81" s="202"/>
+      <c r="H81" s="202"/>
+      <c r="I81" s="202"/>
+      <c r="J81" s="202"/>
+      <c r="K81" s="202"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C82" s="197"/>
-      <c r="D82" s="194"/>
-      <c r="E82" s="194"/>
+      <c r="C82" s="193"/>
+      <c r="D82" s="195"/>
+      <c r="E82" s="195"/>
       <c r="F82" s="62" t="s">
         <v>471</v>
       </c>
@@ -15202,9 +15205,9 @@
       </c>
     </row>
     <row r="83" spans="3:12" ht="33.5" x14ac:dyDescent="0.25">
-      <c r="C83" s="197"/>
-      <c r="D83" s="194"/>
-      <c r="E83" s="194"/>
+      <c r="C83" s="193"/>
+      <c r="D83" s="195"/>
+      <c r="E83" s="195"/>
       <c r="F83" s="62" t="s">
         <v>477</v>
       </c>
@@ -15225,9 +15228,9 @@
       </c>
     </row>
     <row r="84" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C84" s="197"/>
-      <c r="D84" s="194"/>
-      <c r="E84" s="194"/>
+      <c r="C84" s="193"/>
+      <c r="D84" s="195"/>
+      <c r="E84" s="195"/>
       <c r="F84" s="62" t="s">
         <v>479</v>
       </c>
@@ -15248,9 +15251,9 @@
       </c>
     </row>
     <row r="85" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C85" s="197"/>
-      <c r="D85" s="194"/>
-      <c r="E85" s="194"/>
+      <c r="C85" s="193"/>
+      <c r="D85" s="195"/>
+      <c r="E85" s="195"/>
       <c r="F85" s="62" t="s">
         <v>481</v>
       </c>
@@ -15271,9 +15274,9 @@
       </c>
     </row>
     <row r="86" spans="3:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="C86" s="197"/>
-      <c r="D86" s="194"/>
-      <c r="E86" s="194"/>
+      <c r="C86" s="193"/>
+      <c r="D86" s="195"/>
+      <c r="E86" s="195"/>
       <c r="F86" s="62" t="s">
         <v>483</v>
       </c>
@@ -15294,24 +15297,24 @@
       </c>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C87" s="197"/>
-      <c r="D87" s="194"/>
-      <c r="E87" s="194"/>
-      <c r="F87" s="202" t="s">
+      <c r="C87" s="193"/>
+      <c r="D87" s="195"/>
+      <c r="E87" s="195"/>
+      <c r="F87" s="205" t="s">
         <v>485</v>
       </c>
-      <c r="G87" s="203"/>
-      <c r="H87" s="203"/>
-      <c r="I87" s="203"/>
-      <c r="J87" s="203"/>
-      <c r="K87" s="204"/>
+      <c r="G87" s="206"/>
+      <c r="H87" s="206"/>
+      <c r="I87" s="206"/>
+      <c r="J87" s="206"/>
+      <c r="K87" s="207"/>
     </row>
     <row r="96" spans="3:12" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C96" s="197"/>
-      <c r="D96" s="195" t="s">
+      <c r="C96" s="193"/>
+      <c r="D96" s="204" t="s">
         <v>486</v>
       </c>
-      <c r="E96" s="195"/>
+      <c r="E96" s="204"/>
       <c r="F96"/>
       <c r="G96"/>
       <c r="H96"/>
@@ -15321,9 +15324,9 @@
       <c r="L96"/>
     </row>
     <row r="97" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C97" s="197"/>
-      <c r="D97" s="195"/>
-      <c r="E97" s="195"/>
+      <c r="C97" s="193"/>
+      <c r="D97" s="204"/>
+      <c r="E97" s="204"/>
       <c r="F97"/>
       <c r="G97"/>
       <c r="H97"/>
@@ -15333,281 +15336,281 @@
       <c r="L97"/>
     </row>
     <row r="98" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C98" s="197"/>
-      <c r="D98" s="198"/>
-      <c r="E98" s="198"/>
-      <c r="F98" s="198"/>
-      <c r="G98" s="198"/>
-      <c r="H98" s="198"/>
-      <c r="I98" s="198"/>
-      <c r="J98" s="198"/>
-      <c r="K98" s="198"/>
-      <c r="L98" s="198"/>
+      <c r="C98" s="193"/>
+      <c r="D98" s="194"/>
+      <c r="E98" s="194"/>
+      <c r="F98" s="194"/>
+      <c r="G98" s="194"/>
+      <c r="H98" s="194"/>
+      <c r="I98" s="194"/>
+      <c r="J98" s="194"/>
+      <c r="K98" s="194"/>
+      <c r="L98" s="194"/>
     </row>
     <row r="99" spans="3:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C99" s="197"/>
-      <c r="D99" s="194" t="s">
+      <c r="C99" s="193"/>
+      <c r="D99" s="195" t="s">
         <v>458</v>
       </c>
-      <c r="E99" s="196" t="s">
+      <c r="E99" s="203" t="s">
         <v>459</v>
       </c>
-      <c r="F99" s="201"/>
-      <c r="G99" s="201"/>
-      <c r="H99" s="201"/>
-      <c r="I99" s="201"/>
-      <c r="J99" s="201"/>
-      <c r="K99" s="201"/>
-      <c r="L99" s="201"/>
+      <c r="F99" s="198"/>
+      <c r="G99" s="198"/>
+      <c r="H99" s="198"/>
+      <c r="I99" s="198"/>
+      <c r="J99" s="198"/>
+      <c r="K99" s="198"/>
+      <c r="L99" s="198"/>
     </row>
     <row r="100" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C100" s="197"/>
-      <c r="D100" s="194"/>
-      <c r="E100" s="196"/>
-      <c r="F100" s="201"/>
-      <c r="G100" s="201"/>
-      <c r="H100" s="201"/>
-      <c r="I100" s="201"/>
-      <c r="J100" s="201"/>
-      <c r="K100" s="201"/>
-      <c r="L100" s="201"/>
+      <c r="C100" s="193"/>
+      <c r="D100" s="195"/>
+      <c r="E100" s="203"/>
+      <c r="F100" s="198"/>
+      <c r="G100" s="198"/>
+      <c r="H100" s="198"/>
+      <c r="I100" s="198"/>
+      <c r="J100" s="198"/>
+      <c r="K100" s="198"/>
+      <c r="L100" s="198"/>
     </row>
     <row r="101" spans="3:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C101" s="197"/>
-      <c r="D101" s="194" t="s">
+      <c r="C101" s="193"/>
+      <c r="D101" s="195" t="s">
         <v>460</v>
       </c>
-      <c r="E101" s="193" t="s">
+      <c r="E101" s="197" t="s">
         <v>461</v>
       </c>
-      <c r="F101" s="201"/>
-      <c r="G101" s="201"/>
-      <c r="H101" s="201"/>
-      <c r="I101" s="201"/>
-      <c r="J101" s="201"/>
-      <c r="K101" s="201"/>
-      <c r="L101" s="201"/>
+      <c r="F101" s="198"/>
+      <c r="G101" s="198"/>
+      <c r="H101" s="198"/>
+      <c r="I101" s="198"/>
+      <c r="J101" s="198"/>
+      <c r="K101" s="198"/>
+      <c r="L101" s="198"/>
     </row>
     <row r="102" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C102" s="197"/>
-      <c r="D102" s="194"/>
-      <c r="E102" s="193"/>
-      <c r="F102" s="201"/>
-      <c r="G102" s="201"/>
-      <c r="H102" s="201"/>
-      <c r="I102" s="201"/>
-      <c r="J102" s="201"/>
-      <c r="K102" s="201"/>
-      <c r="L102" s="201"/>
+      <c r="C102" s="193"/>
+      <c r="D102" s="195"/>
+      <c r="E102" s="197"/>
+      <c r="F102" s="198"/>
+      <c r="G102" s="198"/>
+      <c r="H102" s="198"/>
+      <c r="I102" s="198"/>
+      <c r="J102" s="198"/>
+      <c r="K102" s="198"/>
+      <c r="L102" s="198"/>
     </row>
     <row r="103" spans="3:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C103" s="197"/>
-      <c r="D103" s="194" t="s">
+      <c r="C103" s="193"/>
+      <c r="D103" s="195" t="s">
         <v>462</v>
       </c>
-      <c r="E103" s="196" t="s">
+      <c r="E103" s="203" t="s">
         <v>463</v>
       </c>
-      <c r="F103" s="201"/>
-      <c r="G103" s="201"/>
-      <c r="H103" s="201"/>
-      <c r="I103" s="201"/>
-      <c r="J103" s="201"/>
-      <c r="K103" s="201"/>
-      <c r="L103" s="201"/>
+      <c r="F103" s="198"/>
+      <c r="G103" s="198"/>
+      <c r="H103" s="198"/>
+      <c r="I103" s="198"/>
+      <c r="J103" s="198"/>
+      <c r="K103" s="198"/>
+      <c r="L103" s="198"/>
     </row>
     <row r="104" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C104" s="197"/>
-      <c r="D104" s="194"/>
-      <c r="E104" s="196"/>
-      <c r="F104" s="201"/>
-      <c r="G104" s="201"/>
-      <c r="H104" s="201"/>
-      <c r="I104" s="201"/>
-      <c r="J104" s="201"/>
-      <c r="K104" s="201"/>
-      <c r="L104" s="201"/>
+      <c r="C104" s="193"/>
+      <c r="D104" s="195"/>
+      <c r="E104" s="203"/>
+      <c r="F104" s="198"/>
+      <c r="G104" s="198"/>
+      <c r="H104" s="198"/>
+      <c r="I104" s="198"/>
+      <c r="J104" s="198"/>
+      <c r="K104" s="198"/>
+      <c r="L104" s="198"/>
     </row>
     <row r="105" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C105" s="197"/>
-      <c r="D105" s="198"/>
-      <c r="E105" s="198"/>
-      <c r="F105" s="198"/>
-      <c r="G105" s="198"/>
-      <c r="H105" s="198"/>
-      <c r="I105" s="198"/>
-      <c r="J105" s="198"/>
-      <c r="K105" s="198"/>
-      <c r="L105" s="198"/>
+      <c r="C105" s="193"/>
+      <c r="D105" s="194"/>
+      <c r="E105" s="194"/>
+      <c r="F105" s="194"/>
+      <c r="G105" s="194"/>
+      <c r="H105" s="194"/>
+      <c r="I105" s="194"/>
+      <c r="J105" s="194"/>
+      <c r="K105" s="194"/>
+      <c r="L105" s="194"/>
     </row>
     <row r="106" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C106" s="197"/>
-      <c r="D106" s="197"/>
-      <c r="E106" s="197"/>
-      <c r="F106" s="197"/>
-      <c r="G106" s="197"/>
-      <c r="H106" s="197"/>
-      <c r="I106" s="197"/>
-      <c r="J106" s="197"/>
-      <c r="K106" s="197"/>
-      <c r="L106" s="197"/>
+      <c r="C106" s="193"/>
+      <c r="D106" s="193"/>
+      <c r="E106" s="193"/>
+      <c r="F106" s="193"/>
+      <c r="G106" s="193"/>
+      <c r="H106" s="193"/>
+      <c r="I106" s="193"/>
+      <c r="J106" s="193"/>
+      <c r="K106" s="193"/>
+      <c r="L106" s="193"/>
     </row>
     <row r="107" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C107" s="197"/>
-      <c r="D107" s="197"/>
-      <c r="E107" s="197"/>
-      <c r="F107" s="197"/>
-      <c r="G107" s="197"/>
-      <c r="H107" s="197"/>
-      <c r="I107" s="197"/>
-      <c r="J107" s="197"/>
-      <c r="K107" s="197"/>
-      <c r="L107" s="197"/>
+      <c r="C107" s="193"/>
+      <c r="D107" s="193"/>
+      <c r="E107" s="193"/>
+      <c r="F107" s="193"/>
+      <c r="G107" s="193"/>
+      <c r="H107" s="193"/>
+      <c r="I107" s="193"/>
+      <c r="J107" s="193"/>
+      <c r="K107" s="193"/>
+      <c r="L107" s="193"/>
     </row>
     <row r="108" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C108" s="197"/>
-      <c r="D108" s="197"/>
-      <c r="E108" s="197"/>
-      <c r="F108" s="197"/>
-      <c r="G108" s="197"/>
-      <c r="H108" s="197"/>
-      <c r="I108" s="197"/>
-      <c r="J108" s="197"/>
-      <c r="K108" s="197"/>
-      <c r="L108" s="197"/>
+      <c r="C108" s="193"/>
+      <c r="D108" s="193"/>
+      <c r="E108" s="193"/>
+      <c r="F108" s="193"/>
+      <c r="G108" s="193"/>
+      <c r="H108" s="193"/>
+      <c r="I108" s="193"/>
+      <c r="J108" s="193"/>
+      <c r="K108" s="193"/>
+      <c r="L108" s="193"/>
     </row>
     <row r="109" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C109" s="197"/>
-      <c r="D109" s="194" t="s">
+      <c r="C109" s="193"/>
+      <c r="D109" s="195" t="s">
         <v>464</v>
       </c>
-      <c r="E109" s="194"/>
-      <c r="F109" s="193">
+      <c r="E109" s="195"/>
+      <c r="F109" s="197">
         <v>1017</v>
       </c>
-      <c r="G109" s="193"/>
-      <c r="H109" s="193"/>
-      <c r="I109" s="193"/>
-      <c r="J109" s="193"/>
-      <c r="K109" s="193"/>
-      <c r="L109" s="193"/>
+      <c r="G109" s="197"/>
+      <c r="H109" s="197"/>
+      <c r="I109" s="197"/>
+      <c r="J109" s="197"/>
+      <c r="K109" s="197"/>
+      <c r="L109" s="197"/>
     </row>
     <row r="110" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C110" s="197"/>
-      <c r="D110" s="194"/>
-      <c r="E110" s="194"/>
-      <c r="F110" s="193"/>
-      <c r="G110" s="193"/>
-      <c r="H110" s="193"/>
-      <c r="I110" s="193"/>
-      <c r="J110" s="193"/>
-      <c r="K110" s="193"/>
-      <c r="L110" s="193"/>
+      <c r="C110" s="193"/>
+      <c r="D110" s="195"/>
+      <c r="E110" s="195"/>
+      <c r="F110" s="197"/>
+      <c r="G110" s="197"/>
+      <c r="H110" s="197"/>
+      <c r="I110" s="197"/>
+      <c r="J110" s="197"/>
+      <c r="K110" s="197"/>
+      <c r="L110" s="197"/>
     </row>
     <row r="111" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C111" s="197"/>
-      <c r="D111" s="194" t="s">
+      <c r="C111" s="193"/>
+      <c r="D111" s="195" t="s">
         <v>465</v>
       </c>
-      <c r="E111" s="194"/>
-      <c r="F111" s="199" t="s">
+      <c r="E111" s="195"/>
+      <c r="F111" s="196" t="s">
         <v>487</v>
       </c>
-      <c r="G111" s="199"/>
-      <c r="H111" s="199"/>
-      <c r="I111" s="199"/>
-      <c r="J111" s="199"/>
-      <c r="K111" s="199"/>
-      <c r="L111" s="199"/>
+      <c r="G111" s="196"/>
+      <c r="H111" s="196"/>
+      <c r="I111" s="196"/>
+      <c r="J111" s="196"/>
+      <c r="K111" s="196"/>
+      <c r="L111" s="196"/>
     </row>
     <row r="112" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C112" s="197"/>
-      <c r="D112" s="194"/>
-      <c r="E112" s="194"/>
-      <c r="F112" s="199"/>
-      <c r="G112" s="199"/>
-      <c r="H112" s="199"/>
-      <c r="I112" s="199"/>
-      <c r="J112" s="199"/>
-      <c r="K112" s="199"/>
-      <c r="L112" s="199"/>
+      <c r="C112" s="193"/>
+      <c r="D112" s="195"/>
+      <c r="E112" s="195"/>
+      <c r="F112" s="196"/>
+      <c r="G112" s="196"/>
+      <c r="H112" s="196"/>
+      <c r="I112" s="196"/>
+      <c r="J112" s="196"/>
+      <c r="K112" s="196"/>
+      <c r="L112" s="196"/>
     </row>
     <row r="113" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C113" s="197"/>
-      <c r="D113" s="194" t="s">
+      <c r="C113" s="193"/>
+      <c r="D113" s="195" t="s">
         <v>467</v>
       </c>
-      <c r="E113" s="194"/>
-      <c r="F113" s="193" t="s">
+      <c r="E113" s="195"/>
+      <c r="F113" s="197" t="s">
         <v>488</v>
       </c>
-      <c r="G113" s="193"/>
-      <c r="H113" s="193"/>
-      <c r="I113" s="193"/>
-      <c r="J113" s="193"/>
-      <c r="K113" s="193"/>
-      <c r="L113" s="193"/>
+      <c r="G113" s="197"/>
+      <c r="H113" s="197"/>
+      <c r="I113" s="197"/>
+      <c r="J113" s="197"/>
+      <c r="K113" s="197"/>
+      <c r="L113" s="197"/>
     </row>
     <row r="114" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C114" s="197"/>
-      <c r="D114" s="194"/>
-      <c r="E114" s="194"/>
-      <c r="F114" s="193"/>
-      <c r="G114" s="193"/>
-      <c r="H114" s="193"/>
-      <c r="I114" s="193"/>
-      <c r="J114" s="193"/>
-      <c r="K114" s="193"/>
-      <c r="L114" s="193"/>
+      <c r="C114" s="193"/>
+      <c r="D114" s="195"/>
+      <c r="E114" s="195"/>
+      <c r="F114" s="197"/>
+      <c r="G114" s="197"/>
+      <c r="H114" s="197"/>
+      <c r="I114" s="197"/>
+      <c r="J114" s="197"/>
+      <c r="K114" s="197"/>
+      <c r="L114" s="197"/>
     </row>
     <row r="115" spans="3:12" ht="168.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C115" s="197"/>
-      <c r="D115" s="194" t="s">
+      <c r="C115" s="193"/>
+      <c r="D115" s="195" t="s">
         <v>469</v>
       </c>
-      <c r="E115" s="194"/>
-      <c r="F115" s="193" t="s">
+      <c r="E115" s="195"/>
+      <c r="F115" s="197" t="s">
         <v>489</v>
       </c>
-      <c r="G115" s="193"/>
-      <c r="H115" s="193"/>
-      <c r="I115" s="193"/>
-      <c r="J115" s="193"/>
-      <c r="K115" s="193"/>
-      <c r="L115" s="193"/>
+      <c r="G115" s="197"/>
+      <c r="H115" s="197"/>
+      <c r="I115" s="197"/>
+      <c r="J115" s="197"/>
+      <c r="K115" s="197"/>
+      <c r="L115" s="197"/>
     </row>
     <row r="116" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C116" s="197"/>
-      <c r="D116" s="194"/>
-      <c r="E116" s="194"/>
-      <c r="F116" s="200"/>
-      <c r="G116" s="200"/>
-      <c r="H116" s="200"/>
-      <c r="I116" s="200"/>
-      <c r="J116" s="200"/>
-      <c r="K116" s="200"/>
-      <c r="L116" s="200"/>
+      <c r="C116" s="193"/>
+      <c r="D116" s="195"/>
+      <c r="E116" s="195"/>
+      <c r="F116" s="202"/>
+      <c r="G116" s="202"/>
+      <c r="H116" s="202"/>
+      <c r="I116" s="202"/>
+      <c r="J116" s="202"/>
+      <c r="K116" s="202"/>
+      <c r="L116" s="202"/>
     </row>
     <row r="117" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C117" s="197"/>
-      <c r="D117" s="194"/>
-      <c r="E117" s="194"/>
+      <c r="C117" s="193"/>
+      <c r="D117" s="195"/>
+      <c r="E117" s="195"/>
       <c r="F117" s="63"/>
-      <c r="G117" s="205" t="s">
+      <c r="G117" s="199" t="s">
         <v>490</v>
       </c>
-      <c r="H117" s="206"/>
-      <c r="I117" s="207"/>
-      <c r="J117" s="205" t="s">
+      <c r="H117" s="200"/>
+      <c r="I117" s="201"/>
+      <c r="J117" s="199" t="s">
         <v>491</v>
       </c>
-      <c r="K117" s="206"/>
-      <c r="L117" s="207"/>
+      <c r="K117" s="200"/>
+      <c r="L117" s="201"/>
     </row>
     <row r="118" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C118" s="197"/>
-      <c r="D118" s="194"/>
-      <c r="E118" s="194"/>
+      <c r="C118" s="193"/>
+      <c r="D118" s="195"/>
+      <c r="E118" s="195"/>
       <c r="F118" s="63"/>
       <c r="G118" s="62" t="s">
         <v>492</v>
@@ -15629,9 +15632,9 @@
       </c>
     </row>
     <row r="119" spans="3:12" ht="20.5" x14ac:dyDescent="0.25">
-      <c r="C119" s="197"/>
-      <c r="D119" s="194"/>
-      <c r="E119" s="194"/>
+      <c r="C119" s="193"/>
+      <c r="D119" s="195"/>
+      <c r="E119" s="195"/>
       <c r="F119" s="63" t="s">
         <v>495</v>
       </c>
@@ -15682,6 +15685,39 @@
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="F74:K75"/>
+    <mergeCell ref="D76:E77"/>
+    <mergeCell ref="D61:E62"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="C61:C87"/>
+    <mergeCell ref="D63:K63"/>
+    <mergeCell ref="D70:K70"/>
+    <mergeCell ref="D96:E97"/>
+    <mergeCell ref="F76:K77"/>
+    <mergeCell ref="D78:E79"/>
+    <mergeCell ref="F78:K79"/>
+    <mergeCell ref="D80:E87"/>
+    <mergeCell ref="F80:K80"/>
+    <mergeCell ref="F81:K81"/>
+    <mergeCell ref="F64:K69"/>
+    <mergeCell ref="F87:K87"/>
+    <mergeCell ref="D71:K71"/>
+    <mergeCell ref="D72:K72"/>
+    <mergeCell ref="D73:K73"/>
+    <mergeCell ref="D74:E75"/>
+    <mergeCell ref="F115:L115"/>
+    <mergeCell ref="F116:L116"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="E101:E102"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="E103:E104"/>
     <mergeCell ref="C96:C119"/>
     <mergeCell ref="D98:L98"/>
     <mergeCell ref="D105:L105"/>
@@ -15698,39 +15734,6 @@
     <mergeCell ref="D109:E110"/>
     <mergeCell ref="F109:L110"/>
     <mergeCell ref="D115:E119"/>
-    <mergeCell ref="F115:L115"/>
-    <mergeCell ref="F116:L116"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="E101:E102"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="E103:E104"/>
-    <mergeCell ref="C61:C87"/>
-    <mergeCell ref="D63:K63"/>
-    <mergeCell ref="D70:K70"/>
-    <mergeCell ref="D96:E97"/>
-    <mergeCell ref="F76:K77"/>
-    <mergeCell ref="D78:E79"/>
-    <mergeCell ref="F78:K79"/>
-    <mergeCell ref="D80:E87"/>
-    <mergeCell ref="F80:K80"/>
-    <mergeCell ref="F81:K81"/>
-    <mergeCell ref="F64:K69"/>
-    <mergeCell ref="F87:K87"/>
-    <mergeCell ref="D71:K71"/>
-    <mergeCell ref="D72:K72"/>
-    <mergeCell ref="D73:K73"/>
-    <mergeCell ref="D74:E75"/>
-    <mergeCell ref="F74:K75"/>
-    <mergeCell ref="D76:E77"/>
-    <mergeCell ref="D61:E62"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -17929,7 +17932,7 @@
         <v>606</v>
       </c>
       <c r="J2" s="83">
-        <v>14.46</v>
+        <v>19.190000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -17955,7 +17958,7 @@
         <v>1346</v>
       </c>
       <c r="J3" s="83">
-        <v>39.229999999999997</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -17981,10 +17984,10 @@
         <v>316</v>
       </c>
       <c r="J4" s="87">
-        <v>4137</v>
+        <v>4023</v>
       </c>
       <c r="K4" s="128" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -18011,7 +18014,7 @@
       </c>
       <c r="J5" s="87">
         <f>J4*J2</f>
-        <v>59821.020000000004</v>
+        <v>77201.37000000001</v>
       </c>
       <c r="L5" s="182"/>
     </row>
@@ -18041,7 +18044,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="128" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="L6" s="87"/>
     </row>
@@ -18068,10 +18071,10 @@
         <v>609</v>
       </c>
       <c r="J7" s="87">
-        <v>13947</v>
+        <v>15613</v>
       </c>
       <c r="K7" s="128" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -18098,7 +18101,7 @@
       </c>
       <c r="J8" s="87">
         <f>J5-J6+J7</f>
-        <v>73768.02</v>
+        <v>92814.37000000001</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -45013,7 +45016,7 @@
       </c>
       <c r="EE121" s="151">
         <f>NPV(EE119,DP113:GB113)+Main!J6-Main!J7</f>
-        <v>94021.814739298978</v>
+        <v>92355.814739298978</v>
       </c>
     </row>
     <row r="122" spans="2:202" s="69" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -45272,7 +45275,7 @@
       <c r="ED122" s="65"/>
       <c r="EE122" s="159">
         <f>+EE121/Main!J4*100</f>
-        <v>2272.7052148730718</v>
+        <v>2295.6951215336558</v>
       </c>
     </row>
     <row r="123" spans="2:202" s="69" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -45428,7 +45431,7 @@
       <c r="DM123" s="70"/>
       <c r="EE123" s="158">
         <f>EE122/1333-1</f>
-        <v>0.70495514994228947</v>
+        <v>0.72220189162314763</v>
       </c>
     </row>
     <row r="124" spans="2:202" ht="13" x14ac:dyDescent="0.3">
@@ -55317,6 +55320,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100764A4B226BE2F34C80DFAA3D37A3CB30" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="70544b0716d1f2dd0e24adda29a3d132">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b05d82d297216baf5b26c55225140df">
     <xsd:element name="properties">
@@ -55430,7 +55439,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -55439,13 +55448,16 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AA8F0A8-F5A8-4CB0-B82B-38561BD2809F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B43E441-751F-4E6B-8948-ECCFE949A7EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -55461,19 +55473,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{574408FA-ABCD-4F72-AAD9-718A64626256}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AA8F0A8-F5A8-4CB0-B82B-38561BD2809F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>